--- a/AAII_Financials/Quarterly/AHEXY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHEXY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
   <si>
     <t>AHEXY</t>
   </si>
@@ -656,60 +656,63 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
-        <v>45565</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45291</v>
-      </c>
-      <c r="K7" s="2">
-        <v>45199</v>
       </c>
       <c r="L7" s="2">
         <v>45291</v>
@@ -718,16 +721,22 @@
         <v>45199</v>
       </c>
       <c r="N7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="O7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -770,8 +779,14 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -814,8 +829,14 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -858,8 +879,14 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +903,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,8 +949,14 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,8 +999,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1008,8 +1049,14 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1052,8 +1099,14 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,8 +1120,10 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1111,8 +1166,14 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1155,8 +1216,14 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1173,8 +1240,10 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1217,8 +1286,14 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1261,8 +1336,14 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1305,8 +1386,14 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1349,8 +1436,14 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1393,8 +1486,14 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1437,8 +1536,14 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1481,8 +1586,14 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1525,8 +1636,14 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1569,8 +1686,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1736,14 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1657,8 +1786,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1701,8 +1836,14 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1745,8 +1886,14 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1789,8 +1936,14 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1833,8 +1986,14 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1877,39 +2036,45 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
-        <v>45565</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
-      </c>
-      <c r="J38" s="2">
-        <v>45291</v>
-      </c>
-      <c r="K38" s="2">
-        <v>45199</v>
       </c>
       <c r="L38" s="2">
         <v>45291</v>
@@ -1918,16 +2083,22 @@
         <v>45199</v>
       </c>
       <c r="N38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="O38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1944,8 +2115,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1962,34 +2135,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>564400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>350500</v>
+      </c>
+      <c r="F41" s="3">
         <v>455600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>401300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>317100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>371800</v>
+      </c>
+      <c r="J41" s="3">
         <v>499000</v>
       </c>
-      <c r="H41" s="3">
-        <v>310100</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>360000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>614600</v>
-      </c>
-      <c r="K41" s="3">
-        <v>388400</v>
       </c>
       <c r="L41" s="3">
         <v>614600</v>
@@ -1998,16 +2173,22 @@
         <v>388400</v>
       </c>
       <c r="N41" s="3">
+        <v>614600</v>
+      </c>
+      <c r="O41" s="3">
+        <v>388400</v>
+      </c>
+      <c r="P41" s="3">
         <v>370100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>662800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>835700</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2050,34 +2231,40 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5256500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5066300</v>
+      </c>
+      <c r="F43" s="3">
         <v>4934800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4954800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5032300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
+        <v>4443400</v>
+      </c>
+      <c r="J43" s="3">
         <v>4264400</v>
       </c>
-      <c r="H43" s="3">
-        <v>4634200</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>4610500</v>
-      </c>
-      <c r="J43" s="3">
-        <v>4937500</v>
-      </c>
-      <c r="K43" s="3">
-        <v>4966100</v>
       </c>
       <c r="L43" s="3">
         <v>4937500</v>
@@ -2086,16 +2273,22 @@
         <v>4966100</v>
       </c>
       <c r="N43" s="3">
+        <v>4937500</v>
+      </c>
+      <c r="O43" s="3">
+        <v>4966100</v>
+      </c>
+      <c r="P43" s="3">
         <v>5165900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>4977200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>5086000</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2138,34 +2331,40 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>573500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>674500</v>
+      </c>
+      <c r="F45" s="3">
         <v>502500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>628900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>579000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
+        <v>617200</v>
+      </c>
+      <c r="J45" s="3">
         <v>422400</v>
       </c>
-      <c r="H45" s="3">
-        <v>581100</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>534700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>459800</v>
-      </c>
-      <c r="K45" s="3">
-        <v>575800</v>
       </c>
       <c r="L45" s="3">
         <v>459800</v>
@@ -2174,42 +2373,48 @@
         <v>575800</v>
       </c>
       <c r="N45" s="3">
+        <v>459800</v>
+      </c>
+      <c r="O45" s="3">
+        <v>575800</v>
+      </c>
+      <c r="P45" s="3">
         <v>575300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>618200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>531200</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6499500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6091300</v>
+      </c>
+      <c r="F46" s="3">
         <v>5958700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5985000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>6010600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>5432300</v>
+      </c>
+      <c r="J46" s="3">
         <v>5259300</v>
       </c>
-      <c r="H46" s="3">
-        <v>5525300</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5584500</v>
-      </c>
-      <c r="J46" s="3">
-        <v>6066100</v>
-      </c>
-      <c r="K46" s="3">
-        <v>5930400</v>
       </c>
       <c r="L46" s="3">
         <v>6066100</v>
@@ -2218,42 +2423,48 @@
         <v>5930400</v>
       </c>
       <c r="N46" s="3">
+        <v>6066100</v>
+      </c>
+      <c r="O46" s="3">
+        <v>5930400</v>
+      </c>
+      <c r="P46" s="3">
         <v>6194300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>6258100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>6544800</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>337000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>294000</v>
+      </c>
+      <c r="F47" s="3">
         <v>304100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>272200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>285400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
+        <v>258300</v>
+      </c>
+      <c r="J47" s="3">
         <v>265000</v>
       </c>
-      <c r="H47" s="3">
-        <v>256500</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>261400</v>
-      </c>
-      <c r="J47" s="3">
-        <v>217800</v>
-      </c>
-      <c r="K47" s="3">
-        <v>207500</v>
       </c>
       <c r="L47" s="3">
         <v>217800</v>
@@ -2262,42 +2473,48 @@
         <v>207500</v>
       </c>
       <c r="N47" s="3">
-        <v>214000</v>
+        <v>217800</v>
       </c>
       <c r="O47" s="3">
         <v>207500</v>
       </c>
       <c r="P47" s="3">
+        <v>214000</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>207500</v>
+      </c>
+      <c r="R47" s="3">
         <v>197700</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1040000</v>
+      </c>
+      <c r="F48" s="3">
         <v>777300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1061800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1086300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
+        <v>1033300</v>
+      </c>
+      <c r="J48" s="3">
         <v>728900</v>
       </c>
-      <c r="H48" s="3">
-        <v>1095200</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1044700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>827900</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1083800</v>
       </c>
       <c r="L48" s="3">
         <v>827900</v>
@@ -2306,42 +2523,48 @@
         <v>1083800</v>
       </c>
       <c r="N48" s="3">
+        <v>827900</v>
+      </c>
+      <c r="O48" s="3">
+        <v>1083800</v>
+      </c>
+      <c r="P48" s="3">
         <v>1121200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1099500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>766300</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5525000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5579400</v>
+      </c>
+      <c r="F49" s="3">
         <v>5938700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>5654100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>5660600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
+        <v>5396700</v>
+      </c>
+      <c r="J49" s="3">
         <v>5514000</v>
       </c>
-      <c r="H49" s="3">
-        <v>5523100</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>5390500</v>
-      </c>
-      <c r="J49" s="3">
-        <v>5889200</v>
-      </c>
-      <c r="K49" s="3">
-        <v>5422300</v>
       </c>
       <c r="L49" s="3">
         <v>5889200</v>
@@ -2350,16 +2573,22 @@
         <v>5422300</v>
       </c>
       <c r="N49" s="3">
+        <v>5889200</v>
+      </c>
+      <c r="O49" s="3">
+        <v>5422300</v>
+      </c>
+      <c r="P49" s="3">
         <v>5544800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>5568200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>5845900</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2402,8 +2631,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2446,34 +2681,40 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>826000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>855500</v>
+      </c>
+      <c r="F52" s="3">
         <v>536600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>860000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>872600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
+        <v>836600</v>
+      </c>
+      <c r="J52" s="3">
         <v>489700</v>
       </c>
-      <c r="H52" s="3">
-        <v>835400</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>721100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>497400</v>
-      </c>
-      <c r="K52" s="3">
-        <v>794900</v>
       </c>
       <c r="L52" s="3">
         <v>497400</v>
@@ -2482,16 +2723,22 @@
         <v>794900</v>
       </c>
       <c r="N52" s="3">
+        <v>497400</v>
+      </c>
+      <c r="O52" s="3">
+        <v>794900</v>
+      </c>
+      <c r="P52" s="3">
         <v>782800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>804000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>532200</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2534,34 +2781,40 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14188300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13860300</v>
+      </c>
+      <c r="F54" s="3">
         <v>13803000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>13833200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>13915400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>12957200</v>
+      </c>
+      <c r="J54" s="3">
         <v>12526100</v>
       </c>
-      <c r="H54" s="3">
-        <v>13235600</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>13002300</v>
-      </c>
-      <c r="J54" s="3">
-        <v>13739400</v>
-      </c>
-      <c r="K54" s="3">
-        <v>13438800</v>
       </c>
       <c r="L54" s="3">
         <v>13739400</v>
@@ -2570,16 +2823,22 @@
         <v>13438800</v>
       </c>
       <c r="N54" s="3">
+        <v>13739400</v>
+      </c>
+      <c r="O54" s="3">
+        <v>13438800</v>
+      </c>
+      <c r="P54" s="3">
         <v>13857000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>13937400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>14166900</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2596,8 +2855,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2614,34 +2875,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5230200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5201200</v>
+      </c>
+      <c r="F57" s="3">
         <v>1100200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4977100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>5012300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
+        <v>4472500</v>
+      </c>
+      <c r="J57" s="3">
         <v>783700</v>
       </c>
-      <c r="H57" s="3">
-        <v>4596300</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>4535500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>919600</v>
-      </c>
-      <c r="K57" s="3">
-        <v>4888900</v>
       </c>
       <c r="L57" s="3">
         <v>919600</v>
@@ -2650,42 +2913,48 @@
         <v>4888900</v>
       </c>
       <c r="N57" s="3">
+        <v>919600</v>
+      </c>
+      <c r="O57" s="3">
+        <v>4888900</v>
+      </c>
+      <c r="P57" s="3">
         <v>4929000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4845700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1241900</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>354200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>539600</v>
+      </c>
+      <c r="F58" s="3">
         <v>359300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>794300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>804500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
+        <v>632300</v>
+      </c>
+      <c r="J58" s="3">
         <v>507300</v>
       </c>
-      <c r="H58" s="3">
-        <v>885600</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>995400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>801400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>286800</v>
       </c>
       <c r="L58" s="3">
         <v>801400</v>
@@ -2694,42 +2963,48 @@
         <v>286800</v>
       </c>
       <c r="N58" s="3">
+        <v>801400</v>
+      </c>
+      <c r="O58" s="3">
+        <v>286800</v>
+      </c>
+      <c r="P58" s="3">
         <v>551300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>356400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>336600</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
         <v>118600</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
         <v>4700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>156300</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>61100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>127100</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="L59" s="3">
         <v>127100</v>
@@ -2738,42 +3013,48 @@
         <v>4</v>
       </c>
       <c r="N59" s="3">
+        <v>127100</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>52400</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>135700</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5641500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5740800</v>
+      </c>
+      <c r="F60" s="3">
         <v>5652200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5771400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5821500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>5104800</v>
+      </c>
+      <c r="J60" s="3">
         <v>4946700</v>
       </c>
-      <c r="H60" s="3">
-        <v>5481800</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5592000</v>
-      </c>
-      <c r="J60" s="3">
-        <v>5657100</v>
-      </c>
-      <c r="K60" s="3">
-        <v>5175700</v>
       </c>
       <c r="L60" s="3">
         <v>5657100</v>
@@ -2782,42 +3063,48 @@
         <v>5175700</v>
       </c>
       <c r="N60" s="3">
+        <v>5657100</v>
+      </c>
+      <c r="O60" s="3">
+        <v>5175700</v>
+      </c>
+      <c r="P60" s="3">
         <v>5532800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>5202100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>5555200</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3874100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3302200</v>
+      </c>
+      <c r="F61" s="3">
         <v>3468400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3354500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3569000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
+        <v>3213400</v>
+      </c>
+      <c r="J61" s="3">
         <v>3177300</v>
       </c>
-      <c r="H61" s="3">
-        <v>3265700</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3195100</v>
-      </c>
-      <c r="J61" s="3">
-        <v>3347000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>3603900</v>
       </c>
       <c r="L61" s="3">
         <v>3347000</v>
@@ -2826,42 +3113,48 @@
         <v>3603900</v>
       </c>
       <c r="N61" s="3">
+        <v>3347000</v>
+      </c>
+      <c r="O61" s="3">
+        <v>3603900</v>
+      </c>
+      <c r="P61" s="3">
         <v>3821000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3691900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3709500</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>668300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>769100</v>
+      </c>
+      <c r="F62" s="3">
         <v>362800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>835400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>761000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
+        <v>803100</v>
+      </c>
+      <c r="J62" s="3">
         <v>376900</v>
       </c>
-      <c r="H62" s="3">
-        <v>745000</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>621500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>417800</v>
-      </c>
-      <c r="K62" s="3">
-        <v>785400</v>
       </c>
       <c r="L62" s="3">
         <v>417800</v>
@@ -2870,16 +3163,22 @@
         <v>785400</v>
       </c>
       <c r="N62" s="3">
+        <v>417800</v>
+      </c>
+      <c r="O62" s="3">
+        <v>785400</v>
+      </c>
+      <c r="P62" s="3">
         <v>685600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>811600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>323800</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2922,8 +3221,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2966,8 +3271,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3010,34 +3321,40 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10183900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>9812100</v>
+      </c>
+      <c r="F66" s="3">
         <v>9815700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>9961300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>10151500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
+        <v>9121300</v>
+      </c>
+      <c r="J66" s="3">
         <v>8813500</v>
       </c>
-      <c r="H66" s="3">
-        <v>9492500</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>9408600</v>
-      </c>
-      <c r="J66" s="3">
-        <v>9759000</v>
-      </c>
-      <c r="K66" s="3">
-        <v>9565000</v>
       </c>
       <c r="L66" s="3">
         <v>9759000</v>
@@ -3046,16 +3363,22 @@
         <v>9565000</v>
       </c>
       <c r="N66" s="3">
+        <v>9759000</v>
+      </c>
+      <c r="O66" s="3">
+        <v>9565000</v>
+      </c>
+      <c r="P66" s="3">
         <v>10039300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>9705600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>10006400</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3072,8 +3395,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3116,8 +3441,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3160,8 +3491,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3204,8 +3541,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3248,34 +3591,40 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3795300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3987100</v>
+      </c>
+      <c r="F72" s="3">
         <v>3977900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3871900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3771000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
+        <v>3598100</v>
+      </c>
+      <c r="J72" s="3">
         <v>3384400</v>
       </c>
-      <c r="H72" s="3">
-        <v>3564600</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3318300</v>
-      </c>
-      <c r="J72" s="3">
-        <v>3755900</v>
-      </c>
-      <c r="K72" s="3">
-        <v>3524600</v>
       </c>
       <c r="L72" s="3">
         <v>3755900</v>
@@ -3284,16 +3633,22 @@
         <v>3524600</v>
       </c>
       <c r="N72" s="3">
+        <v>3755900</v>
+      </c>
+      <c r="O72" s="3">
+        <v>3524600</v>
+      </c>
+      <c r="P72" s="3">
         <v>3521800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3778800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3646500</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3336,8 +3691,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +3741,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3424,34 +3791,40 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3994100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4037800</v>
+      </c>
+      <c r="F76" s="3">
         <v>3975600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3861300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3753400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>3825100</v>
+      </c>
+      <c r="J76" s="3">
         <v>3702200</v>
       </c>
-      <c r="H76" s="3">
-        <v>3736300</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3587300</v>
-      </c>
-      <c r="J76" s="3">
-        <v>3973700</v>
-      </c>
-      <c r="K76" s="3">
-        <v>3862200</v>
       </c>
       <c r="L76" s="3">
         <v>3973700</v>
@@ -3460,16 +3833,22 @@
         <v>3862200</v>
       </c>
       <c r="N76" s="3">
+        <v>3973700</v>
+      </c>
+      <c r="O76" s="3">
+        <v>3862200</v>
+      </c>
+      <c r="P76" s="3">
         <v>3804600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4218800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4147700</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3512,39 +3891,45 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
-        <v>45565</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
-      </c>
-      <c r="J80" s="2">
-        <v>45291</v>
-      </c>
-      <c r="K80" s="2">
-        <v>45199</v>
       </c>
       <c r="L80" s="2">
         <v>45291</v>
@@ -3553,16 +3938,22 @@
         <v>45199</v>
       </c>
       <c r="N80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="O80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3605,8 +3996,14 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3623,8 +4020,10 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3632,25 +4031,25 @@
         <v>44600</v>
       </c>
       <c r="E83" s="3">
+        <v>42200</v>
+      </c>
+      <c r="F83" s="3">
+        <v>-44500</v>
+      </c>
+      <c r="G83" s="3">
+        <v>44600</v>
+      </c>
+      <c r="H83" s="3">
         <v>47100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="I83" s="3">
         <v>-27600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="J83" s="3">
         <v>39200</v>
       </c>
-      <c r="H83" s="3">
-        <v>41500</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>41300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>38200</v>
       </c>
       <c r="L83" s="3">
         <v>4300</v>
@@ -3659,16 +4058,22 @@
         <v>38200</v>
       </c>
       <c r="N83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="O83" s="3">
+        <v>38200</v>
+      </c>
+      <c r="P83" s="3">
         <v>35500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>33300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3711,8 +4116,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3755,8 +4166,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3799,8 +4216,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3843,8 +4266,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3887,34 +4316,40 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-205200</v>
+      </c>
+      <c r="F89" s="3">
         <v>558900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>234700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>95100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
+        <v>-155600</v>
+      </c>
+      <c r="J89" s="3">
         <v>508300</v>
       </c>
-      <c r="H89" s="3">
-        <v>135000</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>173600</v>
-      </c>
-      <c r="J89" s="3">
-        <v>350400</v>
-      </c>
-      <c r="K89" s="3">
-        <v>298500</v>
       </c>
       <c r="L89" s="3">
         <v>350400</v>
@@ -3923,16 +4358,22 @@
         <v>298500</v>
       </c>
       <c r="N89" s="3">
+        <v>350400</v>
+      </c>
+      <c r="O89" s="3">
+        <v>298500</v>
+      </c>
+      <c r="P89" s="3">
         <v>87300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-126000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>490500</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3949,34 +4390,36 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-58700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-35200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-34100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="J91" s="3">
         <v>-46600</v>
       </c>
-      <c r="H91" s="3">
-        <v>-43500</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-36400</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-90600</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-34900</v>
       </c>
       <c r="L91" s="3">
         <v>-90600</v>
@@ -3985,16 +4428,22 @@
         <v>-34900</v>
       </c>
       <c r="N91" s="3">
+        <v>-90600</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="P91" s="3">
         <v>-56800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-53200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-70500</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4037,8 +4486,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4081,34 +4536,40 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-68100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-44600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>1200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
+        <v>-65900</v>
+      </c>
+      <c r="J94" s="3">
         <v>-52800</v>
       </c>
-      <c r="H94" s="3">
-        <v>-36800</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-45000</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-38700</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-36000</v>
       </c>
       <c r="L94" s="3">
         <v>-38700</v>
@@ -4117,16 +4578,22 @@
         <v>-36000</v>
       </c>
       <c r="N94" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="O94" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="P94" s="3">
         <v>-67700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-84700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-96200</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4143,35 +4610,37 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>97100</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3">
         <v>206700</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>462900</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4179,16 +4648,22 @@
         <v>4</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3">
         <v>460700</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4231,8 +4706,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4275,8 +4756,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4319,34 +4806,40 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>231900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>177600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-430900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-123200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-99800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
+        <v>102700</v>
+      </c>
+      <c r="J100" s="3">
         <v>-266100</v>
       </c>
-      <c r="H100" s="3">
-        <v>-188500</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-235700</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-123800</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-265700</v>
       </c>
       <c r="L100" s="3">
         <v>-123800</v>
@@ -4355,42 +4848,48 @@
         <v>-265700</v>
       </c>
       <c r="N100" s="3">
+        <v>-123800</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-265700</v>
+      </c>
+      <c r="P100" s="3">
         <v>-290400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>9800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>75900</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="F101" s="3">
+        <v>49700</v>
+      </c>
+      <c r="G101" s="3">
         <v>-6700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="H101" s="3">
         <v>6400</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>20100</v>
       </c>
-      <c r="H101" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-15200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-72700</v>
-      </c>
-      <c r="K101" s="3">
-        <v>52000</v>
       </c>
       <c r="L101" s="3">
         <v>-72700</v>
@@ -4399,42 +4898,48 @@
         <v>52000</v>
       </c>
       <c r="N101" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="O101" s="3">
+        <v>52000</v>
+      </c>
+      <c r="P101" s="3">
         <v>26100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>33300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>229600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-68000</v>
+      </c>
+      <c r="F102" s="3">
         <v>52800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>65700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-84600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
+        <v>-154600</v>
+      </c>
+      <c r="J102" s="3">
         <v>239200</v>
       </c>
-      <c r="H102" s="3">
-        <v>-97000</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-100700</v>
-      </c>
-      <c r="J102" s="3">
-        <v>187900</v>
-      </c>
-      <c r="K102" s="3">
-        <v>16900</v>
       </c>
       <c r="L102" s="3">
         <v>187900</v>
@@ -4443,12 +4948,18 @@
         <v>16900</v>
       </c>
       <c r="N102" s="3">
+        <v>187900</v>
+      </c>
+      <c r="O102" s="3">
+        <v>16900</v>
+      </c>
+      <c r="P102" s="3">
         <v>-272900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-216200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>397600</v>
       </c>
     </row>
